--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="436">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T12:02:06+00:00</t>
+    <t>2026-07-20T15:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -631,10 +631,7 @@
     <t>ServiceRequest.status</t>
   </si>
   <si>
-    <t>draft | active | on-hold | revoked | completed | entered-in-error | unknown</t>
-  </si>
-  <si>
-    <t>The status of the order.</t>
+    <t>Status des Requests – z. B. active, completed, cancelled.</t>
   </si>
   <si>
     <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](http://hl7.org/fhir/R4/event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R4/task.html) resource.</t>
@@ -667,10 +664,10 @@
     <t>ServiceRequest.intent</t>
   </si>
   <si>
-    <t>proposal | plan | directive | order | original-order | reflex-order | filler-order | instance-order | option</t>
-  </si>
-  <si>
-    <t>Whether the request is a proposal, plan, an original order or a reflex order.</t>
+    <t>Absicht</t>
+  </si>
+  <si>
+    <t>Absicht des Requests – z. B. proposal, plan, order.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
@@ -698,10 +695,10 @@
 </t>
   </si>
   <si>
-    <t>Classification of service</t>
-  </si>
-  <si>
-    <t>A code that classifies the service for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
+    <t>Kategorie</t>
+  </si>
+  <si>
+    <t>Kategorisierung des Requests – enthält verpflichtend das Tumorboard-Coding.</t>
   </si>
   <si>
     <t>There may be multiple axis of categorization depending on the context or use case for retrieving or displaying the resource.  The level of granularity is defined by the category concepts in the value set.</t>
@@ -736,6 +733,12 @@
   </si>
   <si>
     <t>tumorboardConsult</t>
+  </si>
+  <si>
+    <t>Tumorboard-Kennzeichnung</t>
+  </si>
+  <si>
+    <t>Kennzeichnung als Tumorboard-Empfehlung – LOINC 85232-7 Tumor board Consult note.</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -812,10 +815,10 @@
 </t>
   </si>
   <si>
-    <t>What is being requested/ordered</t>
-  </si>
-  <si>
-    <t>A code that identifies a particular service (i.e., procedure, diagnostic investigation, or panel of investigations) that have been requested.</t>
+    <t>Leistung</t>
+  </si>
+  <si>
+    <t>Empfohlene Leistung bzw. Prozedur.</t>
   </si>
   <si>
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
@@ -897,10 +900,10 @@
 </t>
   </si>
   <si>
-    <t>Individual or Entity the service is ordered for</t>
-  </si>
-  <si>
-    <t>On whom or what the service is to be performed. This is usually a human patient, but can also be requested on animals, groups of humans or animals, devices such as dialysis machines, or even locations (typically for environmental scans).</t>
+    <t>Patientin/Patient</t>
+  </si>
+  <si>
+    <t>Person, für die die Empfehlung gilt.</t>
   </si>
   <si>
     <t>Request.subject</t>
@@ -1050,10 +1053,10 @@
 </t>
   </si>
   <si>
-    <t>Who/what is requesting service</t>
-  </si>
-  <si>
-    <t>The individual who initiated the request and has responsibility for its activation.</t>
+    <t>Anfordernde/r</t>
+  </si>
+  <si>
+    <t>Person oder Stelle, die die Empfehlung veranlasst hat.</t>
   </si>
   <si>
     <t>This not the dispatcher, but rather who is the authorizer.  This element is not intended to handle delegation which would generally be managed through the Provenance resource.</t>
@@ -1119,10 +1122,10 @@
 </t>
   </si>
   <si>
-    <t>Requested performer</t>
-  </si>
-  <si>
-    <t>The desired performer for doing the requested service.  For example, the surgeon, dermatopathologist, endoscopist, etc.</t>
+    <t>Durchführende/r</t>
+  </si>
+  <si>
+    <t>Für die Umsetzung vorgesehene Person oder Stelle.</t>
   </si>
   <si>
     <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [request-performerOrder extension](http://hl7.org/fhir/R4/extension-request-performerorder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
@@ -3652,13 +3655,13 @@
         <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3684,13 +3687,13 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
@@ -3723,27 +3726,27 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>206</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3769,13 +3772,13 @@
         <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3801,14 +3804,14 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Y18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="Z18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z18" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
       </c>
@@ -3825,7 +3828,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>90</v>
@@ -3840,16 +3843,16 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>133</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>81</v>
@@ -3857,10 +3860,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3883,19 +3886,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -3920,29 +3923,29 @@
         <v>81</v>
       </c>
       <c r="X19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="Y19" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="Y19" t="s" s="2">
+      <c r="Z19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="Z19" t="s" s="2">
+      <c r="AA19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB19" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3960,13 +3963,13 @@
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AM19" t="s" s="2">
-        <v>228</v>
-      </c>
       <c r="AN19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
@@ -3974,13 +3977,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>81</v>
@@ -4002,19 +4005,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4024,7 +4027,7 @@
         <v>81</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>81</v>
@@ -4039,14 +4042,14 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="Y20" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="Y20" t="s" s="2">
+      <c r="Z20" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="Z20" t="s" s="2">
-        <v>224</v>
-      </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
       </c>
@@ -4063,7 +4066,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4081,13 +4084,13 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>228</v>
-      </c>
       <c r="AN20" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>81</v>
@@ -4095,10 +4098,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4124,10 +4127,10 @@
         <v>110</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4135,7 +4138,7 @@
         <v>81</v>
       </c>
       <c r="Q21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="R21" t="s" s="2">
         <v>81</v>
@@ -4156,13 +4159,13 @@
         <v>81</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>81</v>
@@ -4180,7 +4183,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4195,16 +4198,16 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>81</v>
@@ -4212,10 +4215,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4238,70 +4241,70 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="P22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q22" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="R22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="P22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q22" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="R22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4316,13 +4319,13 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4333,14 +4336,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4359,16 +4362,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4394,13 +4397,13 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
@@ -4418,7 +4421,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4433,31 +4436,31 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4476,16 +4479,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4511,13 +4514,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4535,7 +4538,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4544,7 +4547,7 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -4553,24 +4556,24 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4593,17 +4596,17 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -4652,7 +4655,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4670,10 +4673,10 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4684,10 +4687,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4710,13 +4713,13 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4767,7 +4770,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -4782,31 +4785,31 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4825,13 +4828,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4882,7 +4885,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4897,31 +4900,31 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4940,13 +4943,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4997,7 +5000,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5012,27 +5015,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5055,13 +5058,13 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5088,13 +5091,13 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
@@ -5112,7 +5115,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5133,25 +5136,25 @@
         <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5170,13 +5173,13 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5227,7 +5230,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5242,31 +5245,31 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5285,16 +5288,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5344,7 +5347,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5359,31 +5362,31 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5402,16 +5405,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5437,13 +5440,13 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
@@ -5461,7 +5464,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5476,16 +5479,16 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>81</v>
@@ -5493,14 +5496,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5519,16 +5522,16 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5578,7 +5581,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5593,16 +5596,16 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -5610,10 +5613,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5636,13 +5639,13 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5669,13 +5672,13 @@
         <v>81</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>81</v>
@@ -5693,7 +5696,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5714,10 +5717,10 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -5725,10 +5728,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5751,13 +5754,13 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5808,7 +5811,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5829,10 +5832,10 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -5840,10 +5843,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5866,16 +5869,16 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5901,13 +5904,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -5925,7 +5928,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5940,16 +5943,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -5957,10 +5960,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5983,16 +5986,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6042,7 +6045,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6057,16 +6060,16 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6074,10 +6077,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6100,13 +6103,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6157,7 +6160,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6172,13 +6175,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6189,14 +6192,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6215,16 +6218,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6274,7 +6277,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6289,13 +6292,13 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6306,10 +6309,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6332,16 +6335,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6391,7 +6394,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6409,10 +6412,10 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6423,14 +6426,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6449,19 +6452,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6486,13 +6489,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6510,7 +6513,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6528,24 +6531,24 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6568,13 +6571,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6625,7 +6628,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6640,27 +6643,27 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6683,13 +6686,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6740,7 +6743,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6758,10 +6761,10 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -6772,10 +6775,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6798,16 +6801,16 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6857,7 +6860,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6872,13 +6875,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>133</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T15:05:40+00:00</t>
+    <t>2026-07-27T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:12+00:00</t>
+    <t>2026-07-28T00:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:29:57+00:00</t>
+    <t>2026-07-28T09:41:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T09:41:52+00:00</t>
+    <t>2026-07-29T10:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T10:30:12+00:00</t>
+    <t>2026-07-29T11:12:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:12:20+00:00</t>
+    <t>2026-07-29T12:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:51:02+00:00</t>
+    <t>2026-07-31T12:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:16:37+00:00</t>
+    <t>2026-07-31T12:21:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:21:47+00:00</t>
+    <t>2026-07-31T12:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
